--- a/Assets/Resources/Stats/Stats/Player_stats.xlsx
+++ b/Assets/Resources/Stats/Stats/Player_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Ressources\Stats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Linje\Documents\Project\An-Era-of-the-Seas\Assets\Resources\Stats\Stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B349A6C5-42A4-4A8B-830D-BFD68A250EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57896F81-7432-4FC6-BA89-520534944AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,19 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Crit DMG</t>
-  </si>
-  <si>
-    <t>Crit Rate</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>Defense</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>HP</t>
   </si>
@@ -59,7 +47,22 @@
     <t>Coins</t>
   </si>
   <si>
-    <t>Pure Water Drop</t>
+    <t>PWD</t>
+  </si>
+  <si>
+    <t>CritDMG</t>
+  </si>
+  <si>
+    <t>CritRate</t>
+  </si>
+  <si>
+    <t>ATK</t>
+  </si>
+  <si>
+    <t>DEF</t>
+  </si>
+  <si>
+    <t>Storage</t>
   </si>
 </sst>
 </file>
@@ -377,40 +380,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5546875" customWidth="1"/>
+    <col min="8" max="8" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -435,8 +441,11 @@
       <c r="H2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <f t="shared" ref="A3:A34" si="0">A2+1</f>
         <v>2</v>
@@ -446,11 +455,11 @@
         <v>301</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="B3:F12" si="1">INT(C$2 + ($A3 - 1) * ((C$101 - C$2) / 99))</f>
+        <f>INT(C$2 + ($A3 - 1) * ((C$101 - C$2) / 99))</f>
         <v>101</v>
       </c>
       <c r="D3">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="B3:F12" si="1">INT(D$2 + ($A3 - 1) * ((D$101 - D$2) / 99))</f>
         <v>8</v>
       </c>
       <c r="E3">
@@ -467,8 +476,11 @@
       <c r="H3">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -501,8 +513,11 @@
         <f>INT(H$3*(H$101/H$3)^(($A4-2)/98))</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -535,8 +550,11 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -569,8 +587,11 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I6">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -603,8 +624,11 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I7">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -637,8 +661,11 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -671,8 +698,11 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -705,8 +735,11 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -739,8 +772,11 @@
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -773,8 +809,11 @@
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I12">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -807,8 +846,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I13">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -841,8 +883,11 @@
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I14">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -875,8 +920,11 @@
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -909,8 +957,11 @@
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -943,8 +994,11 @@
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -977,8 +1031,11 @@
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1011,8 +1068,11 @@
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1045,8 +1105,11 @@
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1079,8 +1142,11 @@
         <f t="shared" si="2"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1113,8 +1179,11 @@
         <f t="shared" si="2"/>
         <v>42</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1147,8 +1216,11 @@
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1181,8 +1253,11 @@
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -1215,8 +1290,11 @@
         <f t="shared" si="2"/>
         <v>59</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -1249,8 +1327,11 @@
         <f t="shared" si="2"/>
         <v>66</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -1283,8 +1364,11 @@
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -1317,8 +1401,11 @@
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -1351,8 +1438,11 @@
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I29">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -1385,8 +1475,11 @@
         <f t="shared" si="2"/>
         <v>103</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -1419,8 +1512,11 @@
         <f t="shared" si="2"/>
         <v>115</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -1453,8 +1549,11 @@
         <f t="shared" si="2"/>
         <v>129</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -1487,8 +1586,11 @@
         <f t="shared" si="2"/>
         <v>145</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -1521,8 +1623,11 @@
         <f t="shared" si="2"/>
         <v>162</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35">
         <f t="shared" ref="A35:A66" si="6">A34+1</f>
         <v>34</v>
@@ -1555,8 +1660,11 @@
         <f t="shared" si="2"/>
         <v>181</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36">
         <f t="shared" si="6"/>
         <v>35</v>
@@ -1589,8 +1697,11 @@
         <f t="shared" si="2"/>
         <v>203</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37">
         <f t="shared" si="6"/>
         <v>36</v>
@@ -1623,8 +1734,11 @@
         <f t="shared" si="2"/>
         <v>227</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38">
         <f t="shared" si="6"/>
         <v>37</v>
@@ -1657,8 +1771,11 @@
         <f t="shared" si="2"/>
         <v>254</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39">
         <f t="shared" si="6"/>
         <v>38</v>
@@ -1691,8 +1808,11 @@
         <f t="shared" si="2"/>
         <v>284</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40">
         <f t="shared" si="6"/>
         <v>39</v>
@@ -1725,8 +1845,11 @@
         <f t="shared" si="2"/>
         <v>318</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41">
         <f t="shared" si="6"/>
         <v>40</v>
@@ -1759,8 +1882,11 @@
         <f t="shared" si="2"/>
         <v>356</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I41">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42">
         <f t="shared" si="6"/>
         <v>41</v>
@@ -1793,8 +1919,11 @@
         <f t="shared" si="2"/>
         <v>398</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I42">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43">
         <f t="shared" si="6"/>
         <v>42</v>
@@ -1827,8 +1956,11 @@
         <f t="shared" si="2"/>
         <v>445</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I43">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44">
         <f t="shared" si="6"/>
         <v>43</v>
@@ -1861,8 +1993,11 @@
         <f t="shared" si="2"/>
         <v>498</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I44">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45">
         <f t="shared" si="6"/>
         <v>44</v>
@@ -1895,8 +2030,11 @@
         <f t="shared" si="2"/>
         <v>558</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I45">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46">
         <f t="shared" si="6"/>
         <v>45</v>
@@ -1929,8 +2067,11 @@
         <f t="shared" si="2"/>
         <v>624</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I46">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47">
         <f t="shared" si="6"/>
         <v>46</v>
@@ -1963,8 +2104,11 @@
         <f t="shared" si="2"/>
         <v>698</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I47">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48">
         <f t="shared" si="6"/>
         <v>47</v>
@@ -1997,8 +2141,11 @@
         <f t="shared" si="2"/>
         <v>781</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I48">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <f t="shared" si="6"/>
         <v>48</v>
@@ -2031,8 +2178,11 @@
         <f t="shared" si="2"/>
         <v>874</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I49">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50">
         <f t="shared" si="6"/>
         <v>49</v>
@@ -2065,8 +2215,11 @@
         <f t="shared" si="2"/>
         <v>978</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I50">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <f t="shared" si="6"/>
         <v>50</v>
@@ -2099,8 +2252,11 @@
         <f t="shared" si="2"/>
         <v>1094</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I51">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52">
         <f t="shared" si="6"/>
         <v>51</v>
@@ -2133,8 +2289,11 @@
         <f t="shared" si="2"/>
         <v>1224</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I52">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53">
         <f t="shared" si="6"/>
         <v>52</v>
@@ -2167,8 +2326,11 @@
         <f t="shared" si="2"/>
         <v>1370</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I53">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54">
         <f t="shared" si="6"/>
         <v>53</v>
@@ -2201,8 +2363,11 @@
         <f t="shared" si="2"/>
         <v>1533</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I54">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55">
         <f t="shared" si="6"/>
         <v>54</v>
@@ -2235,8 +2400,11 @@
         <f t="shared" si="2"/>
         <v>1715</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I55">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56">
         <f t="shared" si="6"/>
         <v>55</v>
@@ -2269,8 +2437,11 @@
         <f t="shared" si="2"/>
         <v>1918</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I56">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57">
         <f t="shared" si="6"/>
         <v>56</v>
@@ -2303,8 +2474,11 @@
         <f t="shared" si="2"/>
         <v>2146</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58">
         <f t="shared" si="6"/>
         <v>57</v>
@@ -2337,8 +2511,11 @@
         <f t="shared" si="2"/>
         <v>2402</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I58">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59">
         <f t="shared" si="6"/>
         <v>58</v>
@@ -2371,8 +2548,11 @@
         <f t="shared" si="2"/>
         <v>2687</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I59">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60">
         <f t="shared" si="6"/>
         <v>59</v>
@@ -2405,8 +2585,11 @@
         <f t="shared" si="2"/>
         <v>3006</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I60">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61">
         <f t="shared" si="6"/>
         <v>60</v>
@@ -2439,8 +2622,11 @@
         <f t="shared" si="2"/>
         <v>3363</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I61">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62">
         <f t="shared" si="6"/>
         <v>61</v>
@@ -2473,8 +2659,11 @@
         <f t="shared" si="2"/>
         <v>3763</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I62">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63">
         <f t="shared" si="6"/>
         <v>62</v>
@@ -2507,8 +2696,11 @@
         <f t="shared" si="2"/>
         <v>4210</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I63">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64">
         <f t="shared" si="6"/>
         <v>63</v>
@@ -2541,8 +2733,11 @@
         <f t="shared" si="2"/>
         <v>4711</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I64">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65">
         <f t="shared" si="6"/>
         <v>64</v>
@@ -2575,8 +2770,11 @@
         <f t="shared" si="2"/>
         <v>5270</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I65">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66">
         <f t="shared" si="6"/>
         <v>65</v>
@@ -2609,8 +2807,11 @@
         <f t="shared" si="2"/>
         <v>5897</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I66">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67">
         <f t="shared" ref="A67:A101" si="10">A66+1</f>
         <v>66</v>
@@ -2643,8 +2844,11 @@
         <f t="shared" si="2"/>
         <v>6597</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I67">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68">
         <f t="shared" si="10"/>
         <v>67</v>
@@ -2677,8 +2881,11 @@
         <f t="shared" si="2"/>
         <v>7381</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I68">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69">
         <f t="shared" si="10"/>
         <v>68</v>
@@ -2711,8 +2918,11 @@
         <f t="shared" si="11"/>
         <v>8258</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I69">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70">
         <f t="shared" si="10"/>
         <v>69</v>
@@ -2745,8 +2955,11 @@
         <f t="shared" si="11"/>
         <v>9239</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I70">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71">
         <f t="shared" si="10"/>
         <v>70</v>
@@ -2779,8 +2992,11 @@
         <f t="shared" si="11"/>
         <v>10337</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I71">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72">
         <f t="shared" si="10"/>
         <v>71</v>
@@ -2813,8 +3029,11 @@
         <f t="shared" si="11"/>
         <v>11565</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I72">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73">
         <f t="shared" si="10"/>
         <v>72</v>
@@ -2847,8 +3066,11 @@
         <f t="shared" si="11"/>
         <v>12940</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I73">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74">
         <f t="shared" si="10"/>
         <v>73</v>
@@ -2881,8 +3103,11 @@
         <f t="shared" si="11"/>
         <v>14477</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I74">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75">
         <f t="shared" si="10"/>
         <v>74</v>
@@ -2915,8 +3140,11 @@
         <f t="shared" si="11"/>
         <v>16197</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I75">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76">
         <f t="shared" si="10"/>
         <v>75</v>
@@ -2949,8 +3177,11 @@
         <f t="shared" si="11"/>
         <v>18121</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I76">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77">
         <f t="shared" si="10"/>
         <v>76</v>
@@ -2983,8 +3214,11 @@
         <f t="shared" si="11"/>
         <v>20275</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I77">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78">
         <f t="shared" si="10"/>
         <v>77</v>
@@ -3017,8 +3251,11 @@
         <f t="shared" si="11"/>
         <v>22683</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I78">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79">
         <f t="shared" si="10"/>
         <v>78</v>
@@ -3051,8 +3288,11 @@
         <f t="shared" si="11"/>
         <v>25379</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I79">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80">
         <f t="shared" si="10"/>
         <v>79</v>
@@ -3085,8 +3325,11 @@
         <f t="shared" si="11"/>
         <v>28394</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I80">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81">
         <f t="shared" si="10"/>
         <v>80</v>
@@ -3119,8 +3362,11 @@
         <f t="shared" si="11"/>
         <v>31767</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I81">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82">
         <f t="shared" si="10"/>
         <v>81</v>
@@ -3153,8 +3399,11 @@
         <f t="shared" si="11"/>
         <v>35542</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I82">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83">
         <f t="shared" si="10"/>
         <v>82</v>
@@ -3187,8 +3436,11 @@
         <f t="shared" si="11"/>
         <v>39765</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I83">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84">
         <f t="shared" si="10"/>
         <v>83</v>
@@ -3221,8 +3473,11 @@
         <f t="shared" si="11"/>
         <v>44489</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I84">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85">
         <f t="shared" si="10"/>
         <v>84</v>
@@ -3255,8 +3510,11 @@
         <f t="shared" si="11"/>
         <v>49775</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I85">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86">
         <f t="shared" si="10"/>
         <v>85</v>
@@ -3289,8 +3547,11 @@
         <f t="shared" si="11"/>
         <v>55689</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I86">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87">
         <f t="shared" si="10"/>
         <v>86</v>
@@ -3323,8 +3584,11 @@
         <f t="shared" si="11"/>
         <v>62305</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I87">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88">
         <f t="shared" si="10"/>
         <v>87</v>
@@ -3357,8 +3621,11 @@
         <f t="shared" si="11"/>
         <v>69708</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I88">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89">
         <f t="shared" si="10"/>
         <v>88</v>
@@ -3391,8 +3658,11 @@
         <f t="shared" si="11"/>
         <v>77990</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I89">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90">
         <f t="shared" si="10"/>
         <v>89</v>
@@ -3425,8 +3695,11 @@
         <f t="shared" si="11"/>
         <v>87256</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I90">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91">
         <f t="shared" si="10"/>
         <v>90</v>
@@ -3459,8 +3732,11 @@
         <f t="shared" si="11"/>
         <v>97623</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I91">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92">
         <f t="shared" si="10"/>
         <v>91</v>
@@ -3493,8 +3769,11 @@
         <f t="shared" si="11"/>
         <v>109222</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I92">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93">
         <f t="shared" si="10"/>
         <v>92</v>
@@ -3527,8 +3806,11 @@
         <f t="shared" si="11"/>
         <v>122199</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I93">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94">
         <f t="shared" si="10"/>
         <v>93</v>
@@ -3561,8 +3843,11 @@
         <f t="shared" si="11"/>
         <v>136717</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I94">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95">
         <f t="shared" si="10"/>
         <v>94</v>
@@ -3595,8 +3880,11 @@
         <f t="shared" si="11"/>
         <v>152961</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I95">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96">
         <f t="shared" si="10"/>
         <v>95</v>
@@ -3629,8 +3917,11 @@
         <f t="shared" si="11"/>
         <v>171134</v>
       </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I96">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97">
         <f t="shared" si="10"/>
         <v>96</v>
@@ -3663,8 +3954,11 @@
         <f t="shared" si="11"/>
         <v>191467</v>
       </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I97">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98">
         <f t="shared" si="10"/>
         <v>97</v>
@@ -3697,8 +3991,11 @@
         <f t="shared" si="11"/>
         <v>214215</v>
       </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I98">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99">
         <f t="shared" si="10"/>
         <v>98</v>
@@ -3731,8 +4028,11 @@
         <f t="shared" si="11"/>
         <v>239666</v>
       </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I99">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100">
         <f t="shared" si="10"/>
         <v>99</v>
@@ -3765,8 +4065,11 @@
         <f t="shared" si="11"/>
         <v>268141</v>
       </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I100">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101">
         <f t="shared" si="10"/>
         <v>100</v>
@@ -3791,6 +4094,9 @@
       </c>
       <c r="H101">
         <v>300000</v>
+      </c>
+      <c r="I101">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
